--- a/config/remc_report_config.xlsx
+++ b/config/remc_report_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20389"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20391"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.2.100.58\d$\wrldc_remc_reports_generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334F1005-D449-4D81-8A23-AE95E4E065F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEE5CD-DCD2-42B8-98C8-45185FE08A38}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="app_config" sheetId="18" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <sheet name="scada_graph_data" sheetId="17" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ists_gen!$A$1:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ists_gen!$A$1:$I$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">remc_graph_data!$A$1:$C$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2598" uniqueCount="519">
   <si>
     <t>name</t>
   </si>
@@ -1478,6 +1478,132 @@
   </si>
   <si>
     <t>WREMCPRI.SCADA02.00062444</t>
+  </si>
+  <si>
+    <t>Srijan_Bhuj_2</t>
+  </si>
+  <si>
+    <t>Sitac_Bhuj_2</t>
+  </si>
+  <si>
+    <t>Bhuj_2 Pooling</t>
+  </si>
+  <si>
+    <t>Bhuj_2</t>
+  </si>
+  <si>
+    <t>GANDHAR</t>
+  </si>
+  <si>
+    <t>GANDHAR Pooling</t>
+  </si>
+  <si>
+    <t>Gandhar</t>
+  </si>
+  <si>
+    <t>Jamkhambalia</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND_AVC</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND_AVC</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR_AVC</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA02.00065809</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA02.00065810</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA01.00002757</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA01.00002754</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA01.00002756</t>
+  </si>
+  <si>
+    <t>WREMCPRI.SCADA02.00061112</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND_R0</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND_16</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND_Act</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND_CUF</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND_R0</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND_16</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND_Act</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND_CUF</t>
+  </si>
+  <si>
+    <t>POWERICA-WIND_WIND_R0</t>
+  </si>
+  <si>
+    <t>POWERICA-WIND_WIND_16</t>
+  </si>
+  <si>
+    <t>POWERICA-WIND_WIND_Act</t>
+  </si>
+  <si>
+    <t>POWERICA-WIND_WIND_CUF</t>
+  </si>
+  <si>
+    <t>KAWAS_SOLAR-SOLAR_SOLAR_R0</t>
+  </si>
+  <si>
+    <t>KAWAS_SOLAR-SOLAR_SOLAR_16</t>
+  </si>
+  <si>
+    <t>KAWAS_SOLAR-SOLAR_SOLAR_Act</t>
+  </si>
+  <si>
+    <t>KAWAS_SOLAR-SOLAR_SOLAR_CUF</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR_R0</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR_16</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR_Act</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR_CUF</t>
+  </si>
+  <si>
+    <t>SRIJAN_MORJAR_BHJ2_W-WIND_WIND</t>
+  </si>
+  <si>
+    <t>SITAC_CHUGGER_BHJ2_W-WIND_WIND</t>
+  </si>
+  <si>
+    <t>POWERICA-WIND_WIND</t>
+  </si>
+  <si>
+    <t>KAWAS_SOLAR-SOLAR_SOLAR</t>
+  </si>
+  <si>
+    <t>GANDHAR_SOLAR-SOLAR_SOLAR</t>
   </si>
 </sst>
 </file>
@@ -1506,7 +1632,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1514,12 +1640,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1533,7 +1668,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2265,7 +2402,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
@@ -2679,220 +2816,226 @@
       <c r="A29" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>342</v>
-      </c>
-      <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
+      <c r="A30" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B31" t="s">
-        <v>439</v>
-      </c>
-      <c r="C31" t="s">
-        <v>437</v>
-      </c>
-      <c r="D31" t="s">
-        <v>440</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
+      <c r="A31" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>341</v>
-      </c>
-      <c r="B32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
+      <c r="A32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
       <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>70</v>
+      <c r="A34" s="7" t="s">
+        <v>479</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>70</v>
+      <c r="A36" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B36" t="s">
+        <v>503</v>
+      </c>
+      <c r="C36" t="s">
+        <v>467</v>
+      </c>
+      <c r="D36" t="s">
+        <v>504</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E37" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>44</v>
+      <c r="A38" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="E38" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>466</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F38" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>17</v>
+      <c r="F39" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>382</v>
-      </c>
-      <c r="C40" t="s">
-        <v>368</v>
-      </c>
-      <c r="D40" t="s">
-        <v>383</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B41" t="s">
-        <v>386</v>
-      </c>
-      <c r="C41" t="s">
-        <v>372</v>
-      </c>
-      <c r="D41" t="s">
-        <v>387</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>380</v>
+        <v>70</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>375</v>
+      <c r="A42" t="s">
+        <v>342</v>
       </c>
       <c r="B42" t="s">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>376</v>
+        <v>113</v>
       </c>
       <c r="D42" t="s">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="E42" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>380</v>
+      <c r="F42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>449</v>
+      <c r="A43" t="s">
+        <v>442</v>
       </c>
       <c r="B43" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="C43" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="D43" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>380</v>
+      <c r="F43" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="4"/>
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -2901,7 +3044,6 @@
       <c r="E45" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -2910,7 +3052,6 @@
       <c r="E46" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
@@ -2919,18 +3060,271 @@
       <c r="E47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B52" t="s">
+        <v>382</v>
+      </c>
+      <c r="C52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D52" t="s">
+        <v>383</v>
+      </c>
+      <c r="E52" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B53" t="s">
+        <v>386</v>
+      </c>
+      <c r="C53" t="s">
+        <v>372</v>
+      </c>
+      <c r="D53" t="s">
+        <v>387</v>
+      </c>
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B54" t="s">
+        <v>390</v>
+      </c>
+      <c r="C54" t="s">
+        <v>376</v>
+      </c>
+      <c r="D54" t="s">
+        <v>391</v>
+      </c>
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B55" t="s">
+        <v>459</v>
+      </c>
+      <c r="C55" t="s">
+        <v>450</v>
+      </c>
+      <c r="D55" t="s">
+        <v>460</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="4"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>379</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="E48" t="s">
+      <c r="B60" s="2"/>
+      <c r="E60" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E62" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>482</v>
+      </c>
+      <c r="E68" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -3195,7 +3589,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
@@ -3624,210 +4018,211 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>342</v>
-      </c>
-      <c r="B30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
+      <c r="A30" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B31" t="s">
-        <v>439</v>
-      </c>
-      <c r="C31" t="s">
-        <v>437</v>
-      </c>
-      <c r="D31" t="s">
-        <v>440</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>43</v>
+      <c r="A31" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>350</v>
-      </c>
-      <c r="B32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>43</v>
+      <c r="A32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="4"/>
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="4"/>
+      <c r="A34" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E35" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="4"/>
+      <c r="A35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="4"/>
+      <c r="A36" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B36" t="s">
+        <v>503</v>
+      </c>
+      <c r="C36" t="s">
+        <v>467</v>
+      </c>
+      <c r="D36" t="s">
+        <v>504</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E37" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E38" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" t="s">
-        <v>43</v>
+      <c r="A38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>70</v>
+        <v>466</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>382</v>
-      </c>
-      <c r="C40" t="s">
-        <v>368</v>
-      </c>
-      <c r="D40" t="s">
-        <v>383</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>380</v>
+        <v>70</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>371</v>
+      <c r="A41" t="s">
+        <v>342</v>
       </c>
       <c r="B41" t="s">
-        <v>386</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>372</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>387</v>
+        <v>111</v>
       </c>
       <c r="E41" t="s">
         <v>5</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>380</v>
+      <c r="F41" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>375</v>
+      <c r="A42" t="s">
+        <v>442</v>
       </c>
       <c r="B42" t="s">
-        <v>390</v>
+        <v>439</v>
       </c>
       <c r="C42" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="D42" t="s">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="E42" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>380</v>
+      <c r="F42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>449</v>
+      <c r="A43" t="s">
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>459</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>450</v>
+        <v>118</v>
       </c>
       <c r="D43" t="s">
-        <v>460</v>
+        <v>116</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>380</v>
+      <c r="F43" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3867,14 +4262,264 @@
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B51" t="s">
+        <v>382</v>
+      </c>
+      <c r="C51" t="s">
+        <v>368</v>
+      </c>
+      <c r="D51" t="s">
+        <v>383</v>
+      </c>
+      <c r="E51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B52" t="s">
+        <v>386</v>
+      </c>
+      <c r="C52" t="s">
+        <v>372</v>
+      </c>
+      <c r="D52" t="s">
+        <v>387</v>
+      </c>
+      <c r="E52" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B53" t="s">
+        <v>390</v>
+      </c>
+      <c r="C53" t="s">
+        <v>376</v>
+      </c>
+      <c r="D53" t="s">
+        <v>391</v>
+      </c>
+      <c r="E53" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B54" t="s">
+        <v>459</v>
+      </c>
+      <c r="C54" t="s">
+        <v>450</v>
+      </c>
+      <c r="D54" t="s">
+        <v>460</v>
+      </c>
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="4"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>379</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E59" t="s">
         <v>76</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F59" s="4" t="s">
         <v>380</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" t="s">
+        <v>76</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>482</v>
+      </c>
+      <c r="E67" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4223,7 +4868,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
@@ -4547,165 +5192,157 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>342</v>
+      <c r="A29" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" t="s">
-        <v>43</v>
+        <v>514</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>442</v>
+      <c r="A30" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>443</v>
-      </c>
-      <c r="D30" t="s">
-        <v>43</v>
+        <v>515</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>350</v>
+      <c r="A31" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>70</v>
+      <c r="A33" s="2" t="s">
+        <v>479</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="4"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>70</v>
+      <c r="A35" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>516</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B36" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>44</v>
+      <c r="A37" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>70</v>
+        <v>466</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>367</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" t="s">
-        <v>393</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>380</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>371</v>
+      <c r="A40" t="s">
+        <v>342</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>394</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>380</v>
+        <v>195</v>
+      </c>
+      <c r="D40" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>375</v>
+      <c r="A41" t="s">
+        <v>442</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>395</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>380</v>
+        <v>443</v>
+      </c>
+      <c r="D41" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>449</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>463</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>380</v>
+        <v>196</v>
+      </c>
+      <c r="D42" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4746,53 +5383,256 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>393</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>394</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B52" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s">
+        <v>395</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>449</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>463</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>379</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B58" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s">
+        <v>517</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
+        <v>518</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B66" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>83</v>
       </c>
-      <c r="B49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>84</v>
       </c>
-      <c r="B50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>85</v>
       </c>
-      <c r="B51" t="s">
-        <v>5</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5951,8 +6791,8 @@
       <c r="A9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="7">
-        <v>17263</v>
+      <c r="B9" s="9">
+        <v>17371.599999999999</v>
       </c>
       <c r="C9" t="s">
         <v>154</v>
@@ -5971,8 +6811,8 @@
       <c r="A10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="7">
-        <v>10794</v>
+      <c r="B10" s="9">
+        <v>12384</v>
       </c>
       <c r="C10" t="s">
         <v>149</v>
@@ -5991,9 +6831,9 @@
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <f>B10+B9</f>
-        <v>28057</v>
+        <v>29755.599999999999</v>
       </c>
       <c r="C11" t="s">
         <v>144</v>
@@ -6031,7 +6871,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -6509,7 +7349,7 @@
         <v>446</v>
       </c>
       <c r="B24" s="2">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>447</v>
@@ -6563,7 +7403,7 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(B16:B24)</f>
-        <v>2112.3000000000002</v>
+        <v>2127.3000000000002</v>
       </c>
       <c r="D27"/>
       <c r="F27" s="4" t="s">
@@ -6583,26 +7423,26 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>465</v>
+      <c r="A29" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="B29" s="4">
-        <v>24.3</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>467</v>
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>485</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
-      </c>
-      <c r="E29" t="s">
-        <v>476</v>
+        <v>490</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>491</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>2</v>
@@ -6612,12 +7452,32 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30"/>
+      <c r="A30" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B30" s="4">
+        <v>172.8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>486</v>
+      </c>
+      <c r="D30" t="s">
+        <v>492</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>493</v>
+      </c>
       <c r="F30" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6628,30 +7488,32 @@
       <c r="F31" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="I31" s="2"/>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="B32" s="4">
-        <f>SUM(B29:B31)</f>
-        <v>24.3</v>
+        <v>70</v>
       </c>
       <c r="D32"/>
       <c r="F32" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>468</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I32" s="2"/>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>70</v>
+      <c r="A33" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B33" s="4">
+        <f>B30+B29</f>
+        <v>253.8</v>
       </c>
       <c r="D33"/>
       <c r="F33" s="4" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6665,11 +7527,31 @@
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35"/>
+        <v>465</v>
+      </c>
+      <c r="B35" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D35" t="s">
+        <v>469</v>
+      </c>
+      <c r="E35" t="s">
+        <v>476</v>
+      </c>
       <c r="F35" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -6690,319 +7572,244 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="F38" s="2" t="s">
-        <v>17</v>
+        <v>466</v>
+      </c>
+      <c r="B38" s="4">
+        <f>SUM(B35:B37)</f>
+        <v>50.6</v>
+      </c>
+      <c r="D38"/>
+      <c r="F38" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="D39"/>
       <c r="F39" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B40" s="4">
-        <v>250</v>
-      </c>
-      <c r="C40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" t="s">
-        <v>279</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D40"/>
       <c r="F40" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B41" s="4">
-        <v>250</v>
-      </c>
-      <c r="C41" t="s">
-        <v>437</v>
-      </c>
-      <c r="D41" t="s">
-        <v>280</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>19</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D41"/>
       <c r="F41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B42" s="4">
-        <v>250</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>281</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>20</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D42"/>
       <c r="F42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C43"/>
       <c r="D43"/>
       <c r="F43" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="F44" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="2"/>
+      <c r="D44" s="4"/>
+      <c r="F44" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C45"/>
-      <c r="D45"/>
       <c r="F45" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46"/>
-      <c r="D46"/>
+        <v>333</v>
+      </c>
+      <c r="B46" s="4">
+        <v>250</v>
+      </c>
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" t="s">
+        <v>279</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="F46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47"/>
-      <c r="D47"/>
+        <v>436</v>
+      </c>
+      <c r="B47" s="4">
+        <v>250</v>
+      </c>
+      <c r="C47" t="s">
+        <v>437</v>
+      </c>
+      <c r="D47" t="s">
+        <v>280</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="F47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>44</v>
+        <v>332</v>
       </c>
       <c r="B48" s="4">
-        <f>SUM(B40:B42)</f>
-        <v>750</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+        <v>250</v>
+      </c>
+      <c r="C48" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" t="s">
+        <v>281</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="F48" s="4" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H48" s="2"/>
+      <c r="H48" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="49" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="C49"/>
       <c r="D49"/>
       <c r="F49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="50" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B50" s="4">
-        <v>100</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D50" t="s">
-        <v>369</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>378</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C50"/>
+      <c r="D50"/>
       <c r="F50" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I50" s="2"/>
     </row>
     <row r="51" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B51" s="4">
-        <v>100</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D51" t="s">
-        <v>373</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>374</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C51"/>
+      <c r="D51"/>
       <c r="F51" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I51" s="2"/>
     </row>
     <row r="52" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B52" s="4">
-        <v>200</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="D52" t="s">
-        <v>377</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>370</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C52"/>
+      <c r="D52"/>
       <c r="F52" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="B53" s="2">
-        <v>62.5</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D53" t="s">
-        <v>451</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>452</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C53"/>
+      <c r="D53"/>
       <c r="F53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54"/>
+        <v>44</v>
+      </c>
+      <c r="B54" s="4">
+        <f>SUM(B46:B48)</f>
+        <v>750</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I54" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
@@ -7012,131 +7819,178 @@
       <c r="F55" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I55" s="2"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D56"/>
+        <v>367</v>
+      </c>
+      <c r="B56" s="4">
+        <v>100</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D56" t="s">
+        <v>369</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>378</v>
+      </c>
       <c r="F56" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I56" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="57" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57"/>
+        <v>371</v>
+      </c>
+      <c r="B57" s="4">
+        <v>100</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D57" t="s">
+        <v>373</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>374</v>
+      </c>
       <c r="F57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="58" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>379</v>
-      </c>
-      <c r="B58" s="2">
-        <f>SUM(B50:B53)</f>
-        <v>462.5</v>
-      </c>
-      <c r="D58"/>
+      <c r="A58" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="4">
+        <v>200</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D58" t="s">
+        <v>377</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>370</v>
+      </c>
       <c r="F58" s="4" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="H58" s="2"/>
+      <c r="H58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="59" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="D59"/>
+        <v>449</v>
+      </c>
+      <c r="B59" s="2">
+        <v>85</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D59" t="s">
+        <v>451</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>452</v>
+      </c>
       <c r="F59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="60" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="B60" s="2">
-        <v>56</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D60" t="s">
-        <v>474</v>
-      </c>
-      <c r="E60" t="s">
-        <v>475</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D60"/>
       <c r="F60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I60" s="2"/>
     </row>
     <row r="61" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="2"/>
       <c r="D61"/>
       <c r="F61" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
     </row>
     <row r="62" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="B62" s="2">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D62"/>
       <c r="F62" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="H62" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="I62" s="2"/>
     </row>
     <row r="63" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="2"/>
       <c r="D63"/>
       <c r="F63" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
     </row>
     <row r="64" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="2"/>
+      <c r="A64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B64" s="2">
+        <f>SUM(B56:B59)</f>
+        <v>485</v>
+      </c>
       <c r="D64"/>
       <c r="F64" s="4" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>380</v>
       </c>
       <c r="H64" s="2"/>
     </row>
@@ -7153,14 +8007,32 @@
     </row>
     <row r="66" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66" s="2"/>
-      <c r="D66"/>
+        <v>470</v>
+      </c>
+      <c r="B66" s="2">
+        <v>56</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D66" t="s">
+        <v>474</v>
+      </c>
+      <c r="E66" t="s">
+        <v>475</v>
+      </c>
       <c r="F66" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H66" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="67" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
@@ -7175,12 +8047,17 @@
     </row>
     <row r="68" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="B68" s="2">
+        <v>56</v>
+      </c>
       <c r="D68"/>
       <c r="F68" s="4" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>472</v>
       </c>
       <c r="H68" s="2"/>
     </row>
@@ -7188,87 +8065,177 @@
       <c r="A69" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="B69" s="2"/>
       <c r="D69"/>
       <c r="F69" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="4">
-        <f>B48+B58+B62</f>
-        <v>1268.5</v>
-      </c>
-      <c r="C70" s="4"/>
-      <c r="D70"/>
-      <c r="E70" s="4"/>
+    <row r="70" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B70" s="2">
+        <v>10</v>
+      </c>
+      <c r="C70" t="s">
+        <v>487</v>
+      </c>
+      <c r="D70" t="s">
+        <v>488</v>
+      </c>
+      <c r="E70" t="s">
+        <v>489</v>
+      </c>
       <c r="F70" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>483</v>
+      </c>
       <c r="H70" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
+      <c r="I70" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="D71"/>
+      <c r="F71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B72" s="2">
+        <f>B71+B70</f>
+        <v>10</v>
+      </c>
+      <c r="D72"/>
+      <c r="F72" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="D73"/>
+      <c r="F73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="2"/>
+      <c r="D74"/>
+      <c r="F74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75"/>
+      <c r="F75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="4">
+        <f>B54+B64+B68+B72</f>
+        <v>1301</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B71" s="4">
-        <f>B27+B14+B32</f>
-        <v>2662.6000000000004</v>
-      </c>
-      <c r="C71" s="4"/>
-      <c r="D71"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4" t="s">
+      <c r="B77" s="4">
+        <f>B27+B14+B33+B38</f>
+        <v>2957.7000000000003</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4" t="s">
+      <c r="G77" s="4"/>
+      <c r="H77" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B72" s="4">
-        <f>B71+B70</f>
-        <v>3931.1000000000004</v>
-      </c>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4" t="s">
+      <c r="B78" s="4">
+        <f>B77+B76</f>
+        <v>4258.7000000000007</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7360,7 +8327,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="4">
-        <v>5285</v>
+        <v>6808</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
@@ -7389,7 +8356,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="4">
-        <v>6797</v>
+        <v>6773</v>
       </c>
       <c r="C7" t="s">
         <v>184</v>
@@ -7419,7 +8386,7 @@
       </c>
       <c r="B8" s="4">
         <f>SUM(B6:B7)</f>
-        <v>12082</v>
+        <v>13581</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>26</v>
@@ -7443,7 +8410,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="4">
-        <v>2630</v>
+        <v>2665</v>
       </c>
       <c r="C10" t="s">
         <v>169</v>
@@ -7502,7 +8469,7 @@
       </c>
       <c r="B12" s="4">
         <f>B10+B11</f>
-        <v>7643</v>
+        <v>7678</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>26</v>
@@ -7606,7 +8573,7 @@
       </c>
       <c r="B18" s="4">
         <f>B7+B11+B15</f>
-        <v>14438</v>
+        <v>14414</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -7621,7 +8588,7 @@
       </c>
       <c r="B19" s="4">
         <f>B6+B10+B14</f>
-        <v>9525</v>
+        <v>11083</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -7636,7 +8603,7 @@
       </c>
       <c r="B20" s="4">
         <f>SUM(B18:B19)</f>
-        <v>23963</v>
+        <v>25497</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>74</v>
@@ -7996,7 +8963,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -8432,7 +9399,7 @@
         <v>446</v>
       </c>
       <c r="B24" s="2">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>448</v>
@@ -8480,7 +9447,7 @@
       </c>
       <c r="B27" s="4">
         <f>SUM(B16:B26)</f>
-        <v>2112.3000000000002</v>
+        <v>2127.3000000000002</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>76</v>
@@ -8505,101 +9472,94 @@
       <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B29" s="4">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>490</v>
+      </c>
       <c r="D29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>333</v>
+      <c r="A30" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="B30" s="4">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>279</v>
+        <v>492</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>43</v>
+        <v>480</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B31" s="4">
-        <v>250</v>
-      </c>
-      <c r="C31" t="s">
-        <v>280</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>351</v>
-      </c>
+      <c r="A31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B32" s="4">
-        <v>250</v>
-      </c>
-      <c r="C32" t="s">
-        <v>281</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>351</v>
-      </c>
+      <c r="A32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="D32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="D33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="4"/>
+      <c r="A33" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B33" s="4">
+        <f>SUM(B29:B32)</f>
+        <v>254</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>480</v>
+      </c>
       <c r="F33" s="4"/>
-      <c r="G33" s="2"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B34" s="4"/>
@@ -8608,60 +9568,73 @@
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="2"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="D35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B35" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="C35" t="s">
+        <v>469</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="2"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="2"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>44</v>
+      <c r="A38" s="2" t="s">
+        <v>466</v>
       </c>
       <c r="B38" s="4">
-        <f>SUM(B30:B32)</f>
-        <v>750</v>
+        <f>SUM(B35:B37)</f>
+        <v>50.6</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4" t="s">
         <v>76</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="F38" s="4"/>
       <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -8669,580 +9642,534 @@
         <v>70</v>
       </c>
       <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="4"/>
-      <c r="F39" s="2"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B40" s="4">
-        <v>100</v>
-      </c>
-      <c r="C40" t="s">
-        <v>369</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B41" s="4">
-        <v>100</v>
-      </c>
-      <c r="C41" t="s">
-        <v>373</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B42" s="4">
-        <v>200</v>
-      </c>
-      <c r="C42" t="s">
-        <v>377</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="B43" s="4">
-        <v>62.5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>451</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="2"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="4"/>
+        <v>333</v>
+      </c>
+      <c r="B45" s="4">
+        <v>250</v>
+      </c>
+      <c r="C45" t="s">
+        <v>279</v>
+      </c>
       <c r="D45" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="4"/>
+        <v>436</v>
+      </c>
+      <c r="B46" s="4">
+        <v>250</v>
+      </c>
+      <c r="C46" t="s">
+        <v>280</v>
+      </c>
       <c r="D46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="4"/>
+        <v>332</v>
+      </c>
+      <c r="B47" s="4">
+        <v>250</v>
+      </c>
+      <c r="C47" t="s">
+        <v>281</v>
+      </c>
       <c r="D47" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>379</v>
-      </c>
-      <c r="B48" s="2">
-        <f>SUM(B40:B47)</f>
-        <v>462.5</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="D48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B50" s="4">
-        <v>1268.5</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>13</v>
+        <v>70</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="D50" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="G50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="B51" s="4">
-        <v>2662.6</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>13</v>
+        <v>70</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="D51" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="2"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="4">
-        <f>B51+B50</f>
-        <v>3931.1</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="D52" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="2" t="s">
-        <v>351</v>
-      </c>
+      <c r="G52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B53" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="B53" s="4">
+        <f>SUM(B45:B47)</f>
+        <v>750</v>
+      </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="4"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B54" s="4">
-        <v>5285</v>
-      </c>
-      <c r="C54" t="s">
-        <v>291</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="4"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>24</v>
+        <v>367</v>
       </c>
       <c r="B55" s="4">
-        <v>6797</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>292</v>
+        <v>369</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>22</v>
+        <v>380</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>25</v>
+        <v>371</v>
       </c>
       <c r="B56" s="4">
-        <f>SUM(B54:B55)</f>
-        <v>12082</v>
-      </c>
-      <c r="C56" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="C56" t="s">
+        <v>373</v>
+      </c>
       <c r="D56" s="4" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
+        <v>375</v>
+      </c>
+      <c r="B57" s="4">
+        <v>200</v>
+      </c>
+      <c r="C57" t="s">
+        <v>377</v>
+      </c>
       <c r="D57" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>46</v>
+        <v>449</v>
       </c>
       <c r="B58" s="4">
-        <v>2630</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>285</v>
+        <v>451</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>354</v>
+        <v>380</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59" s="4">
-        <v>5013</v>
-      </c>
-      <c r="C59" t="s">
-        <v>286</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B60" s="4">
-        <f>B58+B59</f>
-        <v>7643</v>
-      </c>
-      <c r="C60" s="4"/>
+        <v>70</v>
+      </c>
+      <c r="B60" s="4"/>
       <c r="D60" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
+      <c r="G60" s="2"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
       <c r="D61" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
+      <c r="G61" s="2"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="4">
-        <v>1610</v>
-      </c>
-      <c r="C62" t="s">
-        <v>288</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B62" s="4"/>
       <c r="D62" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="2"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="4">
-        <v>2628</v>
-      </c>
-      <c r="C63" t="s">
-        <v>287</v>
+      <c r="A63" t="s">
+        <v>379</v>
+      </c>
+      <c r="B63" s="2">
+        <f>SUM(B55:B62)</f>
+        <v>485</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B64" s="4">
-        <f>B63+B62</f>
-        <v>4238</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B64" s="4"/>
       <c r="D64" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F64" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="2"/>
       <c r="G64" s="4"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65" s="4"/>
+      <c r="A65" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B65" s="2">
+        <v>56</v>
+      </c>
+      <c r="C65" t="s">
+        <v>474</v>
+      </c>
       <c r="D65" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B66" s="4">
-        <f>B55+B59+B63</f>
-        <v>14438</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>13</v>
+        <v>70</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E66" s="4"/>
-      <c r="F66" s="4" t="s">
-        <v>356</v>
-      </c>
+      <c r="F66" s="2"/>
       <c r="G66" s="4"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="4">
-        <f>B54+B58+B62</f>
-        <v>9525</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="2" t="s">
-        <v>354</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="B67" s="2">
+        <f>SUM(B65:B66)</f>
+        <v>56</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F67" s="2"/>
       <c r="G67" s="4"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="4">
-        <f>SUM(B66:B67)</f>
-        <v>23963</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="D68" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="2" t="s">
-        <v>355</v>
-      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="4"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="4"/>
+      <c r="A69" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B69" s="2">
+        <v>10</v>
+      </c>
+      <c r="C69" t="s">
+        <v>488</v>
+      </c>
       <c r="D69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="4">
-        <f>regional_profile!B9</f>
-        <v>17263</v>
-      </c>
-      <c r="C70" t="s">
-        <v>283</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B70" s="4"/>
       <c r="D70" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="4"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="4">
-        <f>regional_profile!B10</f>
-        <v>10794</v>
-      </c>
-      <c r="C71" t="s">
-        <v>284</v>
+      <c r="A71" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B71" s="2">
+        <f>SUM(B69:B70)</f>
+        <v>10</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="4"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="4">
-        <f>B71+B70</f>
-        <v>28057</v>
-      </c>
-      <c r="C72" t="s">
-        <v>282</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B72" s="4"/>
       <c r="D72" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="4"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
@@ -9252,114 +10179,455 @@
       <c r="D73" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="4"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
-      <c r="D74" s="4"/>
+      <c r="A74" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="D74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="D75" s="4"/>
+      <c r="A75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="D75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="D76" s="4"/>
+      <c r="A76" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="D76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="4"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="4"/>
-      <c r="D77" s="4"/>
+      <c r="A77" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B77" s="4">
+        <f>B71+B67+B63+B53</f>
+        <v>1301</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G77" s="4"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="4"/>
-      <c r="D78" s="4"/>
+      <c r="A78" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B78" s="4">
+        <f>B38+B33+B27+B14</f>
+        <v>2957.9</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G78" s="4"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="4"/>
-      <c r="D79" s="4"/>
+      <c r="A79" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B79" s="4">
+        <f>B78+B77</f>
+        <v>4258.8999999999996</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="2" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="4"/>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="4"/>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="4"/>
-      <c r="D83" s="4"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="4"/>
-      <c r="D84" s="4"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="4"/>
-      <c r="D85" s="4"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="4"/>
-      <c r="D86" s="4"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-      <c r="D87" s="4"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="4"/>
-      <c r="D88" s="4"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="4"/>
-      <c r="D89" s="4"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-      <c r="D90" s="4"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="4"/>
-      <c r="D91" s="4"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="D92" s="4"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-      <c r="D93" s="4"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="4"/>
-      <c r="D94" s="4"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="4"/>
-      <c r="D95" s="4"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="4"/>
-      <c r="D96" s="4"/>
+      <c r="A80" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" s="4">
+        <v>6808</v>
+      </c>
+      <c r="C81" t="s">
+        <v>291</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" s="4">
+        <v>6773</v>
+      </c>
+      <c r="C82" t="s">
+        <v>292</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" s="4">
+        <f>SUM(B81:B82)</f>
+        <v>13581</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" s="4">
+        <v>2665</v>
+      </c>
+      <c r="C85" t="s">
+        <v>285</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B86" s="4">
+        <v>5013</v>
+      </c>
+      <c r="C86" t="s">
+        <v>286</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B87" s="4">
+        <f>B85+B86</f>
+        <v>7678</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B89" s="4">
+        <v>1610</v>
+      </c>
+      <c r="C89" t="s">
+        <v>288</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" s="4">
+        <v>2628</v>
+      </c>
+      <c r="C90" t="s">
+        <v>287</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B91" s="4">
+        <f>B90+B89</f>
+        <v>4238</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="D92" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B93" s="4">
+        <f>B82+B86+B90</f>
+        <v>14414</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B94" s="4">
+        <f>B81+B85+B89</f>
+        <v>11083</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B95" s="4">
+        <f>SUM(B93:B94)</f>
+        <v>25497</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="D96" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="4"/>
-      <c r="D97" s="4"/>
+      <c r="A97" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="4">
+        <f>regional_profile!B9</f>
+        <v>17371.599999999999</v>
+      </c>
+      <c r="C97" t="s">
+        <v>283</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="4"/>
-      <c r="D98" s="4"/>
+      <c r="A98" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" s="4">
+        <f>regional_profile!B10</f>
+        <v>12384</v>
+      </c>
+      <c r="C98" t="s">
+        <v>284</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="4"/>
-      <c r="D99" s="4"/>
+      <c r="A99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B99" s="4">
+        <f>B98+B97</f>
+        <v>29755.599999999999</v>
+      </c>
+      <c r="C99" t="s">
+        <v>282</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="4"/>
-      <c r="D100" s="4"/>
+      <c r="A100" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="D100" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="4"/>
@@ -9379,122 +10647,149 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="4"/>
+      <c r="D105" s="4"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
+      <c r="D106" s="4"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
+      <c r="D107" s="4"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
+      <c r="D108" s="4"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="4"/>
+      <c r="D109" s="4"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="4"/>
+      <c r="D110" s="4"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
+      <c r="D111" s="4"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D112" s="4"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D113" s="4"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D114" s="4"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D115" s="4"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="4"/>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D116" s="4"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="4"/>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D117" s="4"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D118" s="4"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="4"/>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D119" s="4"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D120" s="4"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="4"/>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D121" s="4"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="4"/>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D122" s="4"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="4"/>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D123" s="4"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D124" s="4"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="4"/>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D125" s="4"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4"/>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D126" s="4"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="4"/>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D127" s="4"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="4"/>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D128" s="4"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="4"/>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D129" s="4"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="4"/>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D130" s="4"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="4"/>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D131" s="4"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="4"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="4"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="4"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="4"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="4"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="4"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="4"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="4"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="4"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="4"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
@@ -9520,6 +10815,87 @@
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="4"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="4"/>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="4"/>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="4"/>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="4"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="4"/>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="4"/>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="4"/>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="4"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="4"/>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="4"/>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="4"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="4"/>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="4"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="4"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="4"/>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="4"/>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="4"/>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="4"/>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="4"/>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="4"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="4"/>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="4"/>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10145,7 +11521,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
@@ -10670,97 +12046,92 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>342</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" t="s">
-        <v>5</v>
-      </c>
-      <c r="H30" t="s">
-        <v>43</v>
+      <c r="A30" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>442</v>
-      </c>
-      <c r="B31" t="s">
-        <v>438</v>
-      </c>
-      <c r="C31" t="s">
-        <v>439</v>
-      </c>
-      <c r="D31" t="s">
-        <v>440</v>
-      </c>
-      <c r="E31" t="s">
-        <v>441</v>
-      </c>
-      <c r="F31" t="s">
-        <v>437</v>
-      </c>
-      <c r="G31" t="s">
-        <v>5</v>
-      </c>
-      <c r="H31" t="s">
-        <v>43</v>
+      <c r="A31" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>341</v>
-      </c>
-      <c r="B32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" t="s">
-        <v>117</v>
-      </c>
-      <c r="F32" t="s">
-        <v>118</v>
-      </c>
-      <c r="G32" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" t="s">
-        <v>43</v>
+      <c r="A32" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
       <c r="G33" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>70</v>
+      <c r="A34" t="s">
+        <v>479</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -10770,150 +12141,108 @@
       <c r="G35" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>70</v>
+      <c r="A36" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B36" t="s">
+        <v>502</v>
+      </c>
+      <c r="C36" t="s">
+        <v>503</v>
+      </c>
+      <c r="D36" t="s">
+        <v>504</v>
+      </c>
+      <c r="E36" t="s">
+        <v>505</v>
+      </c>
+      <c r="F36" t="s">
+        <v>467</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G38" t="s">
-        <v>76</v>
-      </c>
-      <c r="H38" t="s">
-        <v>43</v>
-      </c>
+      <c r="A38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+        <v>466</v>
+      </c>
       <c r="G39" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>381</v>
-      </c>
-      <c r="C40" t="s">
-        <v>382</v>
-      </c>
-      <c r="D40" t="s">
-        <v>383</v>
-      </c>
-      <c r="E40" t="s">
-        <v>384</v>
-      </c>
-      <c r="F40" t="s">
-        <v>368</v>
-      </c>
-      <c r="G40" t="s">
-        <v>5</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B41" t="s">
-        <v>385</v>
-      </c>
-      <c r="C41" t="s">
-        <v>386</v>
-      </c>
-      <c r="D41" t="s">
-        <v>387</v>
-      </c>
-      <c r="E41" t="s">
-        <v>388</v>
-      </c>
-      <c r="F41" t="s">
-        <v>372</v>
-      </c>
-      <c r="G41" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B42" t="s">
-        <v>389</v>
-      </c>
-      <c r="C42" t="s">
-        <v>390</v>
-      </c>
-      <c r="D42" t="s">
-        <v>391</v>
-      </c>
-      <c r="E42" t="s">
-        <v>392</v>
-      </c>
-      <c r="F42" t="s">
-        <v>376</v>
-      </c>
-      <c r="G42" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="B43" t="s">
-        <v>458</v>
-      </c>
-      <c r="C43" t="s">
-        <v>459</v>
-      </c>
-      <c r="D43" t="s">
-        <v>460</v>
-      </c>
-      <c r="E43" t="s">
-        <v>461</v>
-      </c>
-      <c r="F43" t="s">
-        <v>450</v>
-      </c>
-      <c r="G43" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>380</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -10953,100 +12282,96 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>379</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+        <v>342</v>
+      </c>
+      <c r="B48" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D48" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" t="s">
+        <v>112</v>
+      </c>
+      <c r="F48" t="s">
+        <v>113</v>
+      </c>
       <c r="G48" t="s">
-        <v>76</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>380</v>
+        <v>5</v>
+      </c>
+      <c r="H48" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="2" t="s">
-        <v>17</v>
+      <c r="A49" t="s">
+        <v>442</v>
+      </c>
+      <c r="B49" t="s">
+        <v>438</v>
+      </c>
+      <c r="C49" t="s">
+        <v>439</v>
+      </c>
+      <c r="D49" t="s">
+        <v>440</v>
+      </c>
+      <c r="E49" t="s">
+        <v>441</v>
+      </c>
+      <c r="F49" t="s">
+        <v>437</v>
+      </c>
+      <c r="G49" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
         <v>5</v>
       </c>
+      <c r="H50" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" t="s">
-        <v>98</v>
-      </c>
-      <c r="G51" t="s">
-        <v>5</v>
+      <c r="A51" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>85</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" t="s">
-        <v>93</v>
-      </c>
-      <c r="G52" t="s">
-        <v>5</v>
+      <c r="A52" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -11056,7 +12381,6 @@
       <c r="G53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -11065,7 +12389,6 @@
       <c r="G54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
@@ -11074,61 +12397,134 @@
       <c r="G55" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="4"/>
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="G56" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
       <c r="G57" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>367</v>
+      </c>
+      <c r="B58" t="s">
+        <v>381</v>
+      </c>
+      <c r="C58" t="s">
+        <v>382</v>
+      </c>
+      <c r="D58" t="s">
+        <v>383</v>
+      </c>
+      <c r="E58" t="s">
+        <v>384</v>
+      </c>
+      <c r="F58" t="s">
+        <v>368</v>
+      </c>
+      <c r="G58" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="4"/>
+        <v>371</v>
+      </c>
+      <c r="B59" t="s">
+        <v>385</v>
+      </c>
+      <c r="C59" t="s">
+        <v>386</v>
+      </c>
+      <c r="D59" t="s">
+        <v>387</v>
+      </c>
+      <c r="E59" t="s">
+        <v>388</v>
+      </c>
+      <c r="F59" t="s">
+        <v>372</v>
+      </c>
+      <c r="G59" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="4"/>
+        <v>375</v>
+      </c>
+      <c r="B60" t="s">
+        <v>389</v>
+      </c>
+      <c r="C60" t="s">
+        <v>390</v>
+      </c>
+      <c r="D60" t="s">
+        <v>391</v>
+      </c>
+      <c r="E60" t="s">
+        <v>392</v>
+      </c>
+      <c r="F60" t="s">
+        <v>376</v>
+      </c>
+      <c r="G60" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H61" s="4"/>
+        <v>449</v>
+      </c>
+      <c r="B61" t="s">
+        <v>458</v>
+      </c>
+      <c r="C61" t="s">
+        <v>459</v>
+      </c>
+      <c r="D61" t="s">
+        <v>460</v>
+      </c>
+      <c r="E61" t="s">
+        <v>461</v>
+      </c>
+      <c r="F61" t="s">
+        <v>450</v>
+      </c>
+      <c r="G61" t="s">
+        <v>5</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -11138,6 +12534,400 @@
         <v>17</v>
       </c>
       <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" s="4"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>379</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G72" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="4"/>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" t="s">
+        <v>76</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="4"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" t="s">
+        <v>101</v>
+      </c>
+      <c r="E79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F79" t="s">
+        <v>103</v>
+      </c>
+      <c r="G79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" t="s">
+        <v>96</v>
+      </c>
+      <c r="E80" t="s">
+        <v>97</v>
+      </c>
+      <c r="F80" t="s">
+        <v>98</v>
+      </c>
+      <c r="G80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" t="s">
+        <v>92</v>
+      </c>
+      <c r="F81" t="s">
+        <v>93</v>
+      </c>
+      <c r="G81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="4"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" s="4"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="4"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/remc_report_config.xlsx
+++ b/config/remc_report_config.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20391"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.2.100.58\d$\wrldc_remc_reports_generator\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wrldc_remc_reports_generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DEE5CD-DCD2-42B8-98C8-45185FE08A38}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" firstSheet="12" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="app_config" sheetId="18" r:id="rId1"/>
@@ -37,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ists_gen!$A$1:$I$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">remc_graph_data!$A$1:$C$56</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1609,7 +1608,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1674,7 +1673,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1985,7 +1984,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2027,7 +2026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2401,7 +2400,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3333,7 +3332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3588,7 +3587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4529,7 +4528,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4776,7 +4775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4867,7 +4866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5642,7 +5641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5915,7 +5914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6585,7 +6584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="42.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6699,7 +6698,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6870,7 +6869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8244,7 +8243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8962,7 +8961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10903,7 +10902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11045,7 +11044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11307,7 +11306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11520,7 +11519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/config/remc_report_config.xlsx
+++ b/config/remc_report_config.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20392"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wrldc_remc_reports_generator\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.2.100.58\d$\wrldc_remc_reports_generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F81C4B-FC67-417B-BDF6-9B62CD5ADE7C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" firstSheet="12" activeTab="17"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="app_config" sheetId="18" r:id="rId1"/>
@@ -36,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ists_gen!$A$1:$I$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">remc_graph_data!$A$1:$C$56</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1608,7 +1609,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1673,7 +1674,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1984,7 +1985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2026,7 +2027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2400,7 +2401,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3332,7 +3333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3587,7 +3588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4528,7 +4529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4775,7 +4776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4866,7 +4867,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5641,7 +5642,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5914,7 +5915,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6584,7 +6585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="42.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6698,7 +6699,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6791,7 +6792,7 @@
         <v>79</v>
       </c>
       <c r="B9" s="9">
-        <v>17371.599999999999</v>
+        <v>17460</v>
       </c>
       <c r="C9" t="s">
         <v>154</v>
@@ -6811,7 +6812,7 @@
         <v>80</v>
       </c>
       <c r="B10" s="9">
-        <v>12384</v>
+        <v>12453</v>
       </c>
       <c r="C10" t="s">
         <v>149</v>
@@ -6832,7 +6833,7 @@
       </c>
       <c r="B11" s="9">
         <f>B10+B9</f>
-        <v>29755.599999999999</v>
+        <v>29913</v>
       </c>
       <c r="C11" t="s">
         <v>144</v>
@@ -6869,7 +6870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7019,7 +7020,7 @@
         <v>405</v>
       </c>
       <c r="B9" s="4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
         <v>414</v>
@@ -7093,7 +7094,7 @@
       </c>
       <c r="B14" s="1">
         <f>SUM(B7:B9)</f>
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D14"/>
       <c r="F14" s="1" t="s">
@@ -7455,7 +7456,7 @@
         <v>478</v>
       </c>
       <c r="B30" s="4">
-        <v>172.8</v>
+        <v>257</v>
       </c>
       <c r="C30" t="s">
         <v>486</v>
@@ -7505,7 +7506,7 @@
       </c>
       <c r="B33" s="4">
         <f>B30+B29</f>
-        <v>253.8</v>
+        <v>338</v>
       </c>
       <c r="D33"/>
       <c r="F33" s="4" t="s">
@@ -7912,7 +7913,7 @@
         <v>449</v>
       </c>
       <c r="B59" s="2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>450</v>
@@ -7982,7 +7983,7 @@
       </c>
       <c r="B64" s="2">
         <f>SUM(B56:B59)</f>
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D64"/>
       <c r="F64" s="4" t="s">
@@ -8166,7 +8167,7 @@
       </c>
       <c r="B76" s="4">
         <f>B54+B64+B68+B72</f>
-        <v>1301</v>
+        <v>1316</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76"/>
@@ -8185,7 +8186,7 @@
       </c>
       <c r="B77" s="4">
         <f>B27+B14+B33+B38</f>
-        <v>2957.7000000000003</v>
+        <v>3045.9</v>
       </c>
       <c r="C77" s="4"/>
       <c r="D77"/>
@@ -8204,7 +8205,7 @@
       </c>
       <c r="B78" s="4">
         <f>B77+B76</f>
-        <v>4258.7000000000007</v>
+        <v>4361.8999999999996</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -8243,7 +8244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8409,7 +8410,7 @@
         <v>46</v>
       </c>
       <c r="B10" s="4">
-        <v>2665</v>
+        <v>2719</v>
       </c>
       <c r="C10" t="s">
         <v>169</v>
@@ -8468,7 +8469,7 @@
       </c>
       <c r="B12" s="4">
         <f>B10+B11</f>
-        <v>7678</v>
+        <v>7732</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>26</v>
@@ -8587,7 +8588,7 @@
       </c>
       <c r="B19" s="4">
         <f>B6+B10+B14</f>
-        <v>11083</v>
+        <v>11137</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -8602,7 +8603,7 @@
       </c>
       <c r="B20" s="4">
         <f>SUM(B18:B19)</f>
-        <v>25497</v>
+        <v>25551</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>74</v>
@@ -8961,7 +8962,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9113,7 +9114,7 @@
         <v>405</v>
       </c>
       <c r="B9" s="4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
         <v>435</v>
@@ -9185,7 +9186,7 @@
       </c>
       <c r="B14" s="4">
         <f>SUM(B7:B9)</f>
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>76</v>
@@ -9498,7 +9499,7 @@
         <v>478</v>
       </c>
       <c r="B30" s="4">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="C30" t="s">
         <v>492</v>
@@ -9546,7 +9547,7 @@
       </c>
       <c r="B33" s="4">
         <f>SUM(B29:B32)</f>
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>76</v>
@@ -9947,7 +9948,7 @@
         <v>449</v>
       </c>
       <c r="B58" s="4">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
         <v>451</v>
@@ -10019,7 +10020,7 @@
       </c>
       <c r="B63" s="2">
         <f>SUM(B55:B62)</f>
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>76</v>
@@ -10224,7 +10225,7 @@
       </c>
       <c r="B77" s="4">
         <f>B71+B67+B63+B53</f>
-        <v>1301</v>
+        <v>1316</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>13</v>
@@ -10241,7 +10242,7 @@
       </c>
       <c r="B78" s="4">
         <f>B38+B33+B27+B14</f>
-        <v>2957.9</v>
+        <v>3045.9</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>13</v>
@@ -10258,7 +10259,7 @@
       </c>
       <c r="B79" s="4">
         <f>B78+B77</f>
-        <v>4258.8999999999996</v>
+        <v>4361.8999999999996</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4" t="s">
@@ -10365,7 +10366,7 @@
         <v>46</v>
       </c>
       <c r="B85" s="4">
-        <v>2665</v>
+        <v>2719</v>
       </c>
       <c r="C85" t="s">
         <v>285</v>
@@ -10412,7 +10413,7 @@
       </c>
       <c r="B87" s="4">
         <f>B85+B86</f>
-        <v>7678</v>
+        <v>7732</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4" t="s">
@@ -10535,7 +10536,7 @@
       </c>
       <c r="B94" s="4">
         <f>B81+B85+B89</f>
-        <v>11083</v>
+        <v>11137</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>13</v>
@@ -10552,7 +10553,7 @@
       </c>
       <c r="B95" s="4">
         <f>SUM(B93:B94)</f>
-        <v>25497</v>
+        <v>25551</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>74</v>
@@ -10580,7 +10581,7 @@
       </c>
       <c r="B97" s="4">
         <f>regional_profile!B9</f>
-        <v>17371.599999999999</v>
+        <v>17460</v>
       </c>
       <c r="C97" t="s">
         <v>283</v>
@@ -10595,7 +10596,7 @@
       </c>
       <c r="B98" s="4">
         <f>regional_profile!B10</f>
-        <v>12384</v>
+        <v>12453</v>
       </c>
       <c r="C98" t="s">
         <v>284</v>
@@ -10610,7 +10611,7 @@
       </c>
       <c r="B99" s="4">
         <f>B98+B97</f>
-        <v>29755.599999999999</v>
+        <v>29913</v>
       </c>
       <c r="C99" t="s">
         <v>282</v>
@@ -10902,7 +10903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11044,7 +11045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11306,7 +11307,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11519,7 +11520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
